--- a/artfynd/A 53652-2024 artfynd.xlsx
+++ b/artfynd/A 53652-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88575266</v>
+        <v>88575497</v>
       </c>
       <c r="B2" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219880</v>
+        <v>3286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bockängena, Jmt</t>
+          <t>Ängsmon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488922.7747144513</v>
+        <v>488706</v>
       </c>
       <c r="R2" t="n">
-        <v>7001948.798424318</v>
+        <v>7001662</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88575497</v>
+        <v>88575266</v>
       </c>
       <c r="B3" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3286</v>
+        <v>219880</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ängsmon, Jmt</t>
+          <t>Bockängena, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488705.8175487169</v>
+        <v>488923</v>
       </c>
       <c r="R3" t="n">
-        <v>7001661.988973655</v>
+        <v>7001949</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88575031</v>
+        <v>88575280</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>219880</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bockängena, Jmt</t>
+          <t>Ängsmon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488923.2150696532</v>
+        <v>488821</v>
       </c>
       <c r="R4" t="n">
-        <v>7001945.179978974</v>
+        <v>7001785</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88575280</v>
+        <v>88575031</v>
       </c>
       <c r="B5" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219880</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ängsmon, Jmt</t>
+          <t>Bockängena, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488820.7955873623</v>
+        <v>488923</v>
       </c>
       <c r="R5" t="n">
-        <v>7001785.026398046</v>
+        <v>7001945</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88575179</v>
+        <v>88575178</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488733.0925577486</v>
+        <v>488845</v>
       </c>
       <c r="R6" t="n">
-        <v>7001693.092619799</v>
+        <v>7001780</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2020-09-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,6 +1157,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>88575179</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ängsmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488733</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7001693</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53652-2024 artfynd.xlsx
+++ b/artfynd/A 53652-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88575497</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88575266</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88575280</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88575031</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88575178</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88575179</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>